--- a/out/07_Ops/SNX-OPS-FRM-08 Technical Ticket Incident Register (Rev00 DRAFT).xlsx
+++ b/out/07_Ops/SNX-OPS-FRM-08 Technical Ticket Incident Register (Rev00 DRAFT).xlsx
@@ -15,7 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Target Severity'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Daftar'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Register'!$A$4:$W$305</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Register'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Ringkasan'!$6:$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -178,7 +182,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -335,6 +339,48 @@
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -729,8 +775,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="28">
-      <c r="A4" s="31" t="inlineStr">
+    <row r="3" s="28">
+      <c r="A3" s="53" t="n"/>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="28">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -740,9 +793,12 @@
           <t>SNX-OPS-FRM-08</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="28">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="53" t="n"/>
+      <c r="E4" s="53" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="28">
+      <c r="A5" s="54" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -752,9 +808,12 @@
           <t>Technical Ticket / Incident Register</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="28">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="C5" s="53" t="n"/>
+      <c r="D5" s="53" t="n"/>
+      <c r="E5" s="53" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="28">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -764,9 +823,12 @@
           <t>00 (Draft)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="28">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="C6" s="53" t="n"/>
+      <c r="D6" s="53" t="n"/>
+      <c r="E6" s="53" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="28">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -776,9 +838,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="28">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="C7" s="53" t="n"/>
+      <c r="D7" s="53" t="n"/>
+      <c r="E7" s="53" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="28">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -788,9 +853,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="28">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="C8" s="53" t="n"/>
+      <c r="D8" s="53" t="n"/>
+      <c r="E8" s="53" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="28">
+      <c r="A9" s="54" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -800,9 +868,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="28">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="C9" s="53" t="n"/>
+      <c r="D9" s="53" t="n"/>
+      <c r="E9" s="53" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="28">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -812,9 +883,12 @@
           <t>Lead NOC</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="28">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="C10" s="53" t="n"/>
+      <c r="D10" s="53" t="n"/>
+      <c r="E10" s="53" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="28">
+      <c r="A11" s="54" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -824,9 +898,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="28">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
+      <c r="E11" s="53" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="28">
+      <c r="A12" s="54" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -836,9 +913,12 @@
           <t>Klausul 8.5.1, 8.7, 9.1.1</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="28">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="53" t="n"/>
+      <c r="E12" s="53" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="28">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -848,9 +928,12 @@
           <t>Kontrol Annex A 5.25, 5.26</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="28">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="C13" s="53" t="n"/>
+      <c r="D13" s="53" t="n"/>
+      <c r="E13" s="53" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="28">
+      <c r="A14" s="54" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -860,140 +943,200 @@
           <t>3 tahun</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="28">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="C14" s="53" t="n"/>
+      <c r="D14" s="53" t="n"/>
+      <c r="E14" s="53" t="n"/>
+    </row>
+    <row r="15" ht="43.5" customHeight="1" s="28">
+      <c r="A15" s="54" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Register seluruh tiket teknis dan insiden dengan waktu Ack dan pemulihan, status SLA, dan tautan RCA sesuai SNX-OPS-SOP-04.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="28">
-      <c r="A17" s="33" t="inlineStr">
+          <t>Register semua ticket teknis dan insiden, berisi waktu Ack dan pemulihan, status SLA, serta tautan RCA, sesuai SNX-OPS-SOP-04.</t>
+        </is>
+      </c>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
+      <c r="E15" s="53" t="n"/>
+    </row>
+    <row r="16" s="28">
+      <c r="A16" s="53" t="n"/>
+      <c r="B16" s="53" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
+      <c r="E16" s="53" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="28">
+      <c r="A17" s="55" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="35.05" customHeight="1" s="28">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="B17" s="53" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
+      <c r="E17" s="53" t="n"/>
+    </row>
+    <row r="18" ht="70.5" customHeight="1" s="28">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Tiket Ops dibuat di Zammad (Nusagrid), tiket generalist di Service Hub GLPI (USULAN, batas menunggu owner). Register ini adalah rekap audit; ekspor dari ticketing system boleh ditempel di sheet Register dengan kolom yang sama.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="28">
-      <c r="A19" s="34" t="inlineStr">
+          <t>Ticket Ops dibuat di Zammad (Nusagrid), sedangkan ticket generalist dibuat di Service Hub GLPI; pembagian ini masih menunggu keputusan owner (USULAN). Register ini adalah rekap audit. Ekspor dari ticketing system boleh ditempel di sheet Register dengan kolom yang sama.</t>
+        </is>
+      </c>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
+      <c r="E18" s="53" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="28">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Isi Severity dulu, lalu waktu dalam format tanggal dan jam (WIB).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="23.85" customHeight="1" s="28">
-      <c r="A20" s="34" t="inlineStr">
+          <t>Isi Severity terlebih dahulu, lalu isi waktu dengan format tanggal dan jam (WIB).</t>
+        </is>
+      </c>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
+      <c r="E19" s="53" t="n"/>
+    </row>
+    <row r="20" ht="43.5" customHeight="1" s="28">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Respon (Dilaporkan sampai Ack), durasi pulih (Dilaporkan sampai Pulih), dan status SLA dihitung otomatis memakai sheet Target Severity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="23.85" customHeight="1" s="28">
-      <c r="A21" s="34" t="inlineStr">
+          <t>Respon (Dilaporkan sampai Ack), durasi pulih (Dilaporkan sampai Pulih), dan status SLA dihitung otomatis berdasarkan sheet Target Severity.</t>
+        </is>
+      </c>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
+      <c r="E20" s="53" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="28">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Kolom RCA wajib otomatis Ya untuk P1 dan P2; isi nomor RCA dari SNX-OPS-FRM-10.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="28">
-      <c r="A23" s="33" t="inlineStr">
+          <t>Kolom RCA wajib otomatis bernilai Ya untuk P1 dan P2. Isi nomor RCA dari SNX-OPS-FRM-10.</t>
+        </is>
+      </c>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
+      <c r="E21" s="53" t="n"/>
+    </row>
+    <row r="22" s="28">
+      <c r="A22" s="53" t="n"/>
+      <c r="B22" s="53" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
+      <c r="E22" s="53" t="n"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="28">
+      <c r="A23" s="55" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="28">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B23" s="53" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
+      <c r="E23" s="53" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="28">
+      <c r="A24" s="56" t="n"/>
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="28">
-      <c r="A25" s="37" t="n"/>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
+      <c r="E24" s="53" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1" s="28">
+      <c r="A25" s="57" t="n"/>
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Biru muda: warna baris contoh, sudah dikosongkan dan tidak dipakai</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="28">
-      <c r="A26" s="38" t="n"/>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
+      <c r="E25" s="53" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="28">
+      <c r="A26" s="58" t="n"/>
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="28">
-      <c r="A28" s="33" t="inlineStr">
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
+      <c r="E26" s="53" t="n"/>
+    </row>
+    <row r="27" s="28">
+      <c r="A27" s="53" t="n"/>
+      <c r="B27" s="53" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
+      <c r="E27" s="53" t="n"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" s="28">
+      <c r="A28" s="55" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="28">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="B28" s="53" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
+      <c r="E28" s="53" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="28">
+      <c r="A29" s="43" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B29" s="39" t="inlineStr">
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C29" s="39" t="inlineStr">
+      <c r="C29" s="43" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D29" s="39" t="inlineStr">
+      <c r="D29" s="43" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E29" s="39" t="inlineStr">
+      <c r="E29" s="43" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="23.85" customHeight="1" s="28">
+    <row r="30" ht="30" customHeight="1" s="28">
       <c r="A30" s="32" t="inlineStr">
         <is>
           <t>00</t>
@@ -1027,76 +1170,91 @@
       <c r="D31" s="32" t="n"/>
       <c r="E31" s="32" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1" s="28">
-      <c r="A33" s="33" t="inlineStr">
+    <row r="32" s="28">
+      <c r="A32" s="53" t="n"/>
+      <c r="B32" s="53" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
+      <c r="E32" s="53" t="n"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="28">
+      <c r="A33" s="55" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="28">
-      <c r="A34" s="39" t="inlineStr">
+      <c r="B33" s="53" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
+      <c r="E33" s="53" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="28">
+      <c r="A34" s="43" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B34" s="39" t="inlineStr">
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C34" s="39" t="inlineStr">
+      <c r="C34" s="43" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D34" s="39" t="inlineStr">
+      <c r="D34" s="43" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E34" s="53" t="n"/>
     </row>
     <row r="35" ht="27.75" customHeight="1" s="28">
-      <c r="A35" s="40" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B35" s="40" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C35" s="40" t="n"/>
-      <c r="D35" s="40" t="n"/>
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="32" t="n"/>
+      <c r="E35" s="53" t="n"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="28">
-      <c r="A36" s="40" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C36" s="40" t="n"/>
-      <c r="D36" s="40" t="n"/>
+      <c r="C36" s="32" t="n"/>
+      <c r="D36" s="32" t="n"/>
+      <c r="E36" s="53" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="28">
-      <c r="A37" s="40" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B37" s="40" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C37" s="40" t="n"/>
-      <c r="D37" s="40" t="n"/>
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="32" t="n"/>
+      <c r="E37" s="53" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1140,7 +1298,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1161,11 +1319,11 @@
     <row r="2" ht="15" customHeight="1" s="28">
       <c r="A2" s="42" t="inlineStr">
         <is>
-          <t>Ack dan update dari SNX-OPS-SOP-04. Target pemulihan = USULAN internal; komitmen ke pelanggan mengikuti kontrak. Jam kerja dihitung sebagai jam kalender untuk penyederhanaan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="28">
+          <t>Target Ack dan update berasal dari SNX-OPS-SOP-04. Target pemulihan adalah USULAN internal, sedangkan komitmen ke pelanggan mengikuti kontrak. Untuk penyederhanaan, jam kerja dihitung sebagai jam kalender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="28">
       <c r="A4" s="43" t="inlineStr">
         <is>
           <t>Severity</t>
@@ -1187,76 +1345,76 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="28">
-      <c r="A5" s="40" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="28">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B5" s="44" t="n">
+      <c r="B5" s="60" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="44" t="n">
+      <c r="C5" s="60" t="n">
         <v>60</v>
       </c>
-      <c r="D5" s="44" t="n">
+      <c r="D5" s="60" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="28">
-      <c r="A6" s="40" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1" s="28">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B6" s="44" t="n">
+      <c r="B6" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="44" t="n">
+      <c r="C6" s="60" t="n">
         <v>180</v>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="60" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="28">
-      <c r="A7" s="40" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1" s="28">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B7" s="44" t="n">
+      <c r="B7" s="60" t="n">
         <v>120</v>
       </c>
-      <c r="C7" s="44" t="n">
+      <c r="C7" s="60" t="n">
         <v>1440</v>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="60" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="28">
-      <c r="A8" s="40" t="inlineStr">
+    <row r="8" ht="16.5" customHeight="1" s="28">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B8" s="44" t="n">
+      <c r="B8" s="60" t="n">
         <v>1440</v>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>Saat selesai</t>
         </is>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="60" t="n">
         <v>72</v>
       </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1264,7 +1422,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1276,185 +1434,204 @@
     <col width="20" customWidth="1" style="27" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="28">
-      <c r="A1" s="45" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="28">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>Ticketing system</t>
         </is>
       </c>
-      <c r="B1" s="45" t="inlineStr">
+      <c r="B1" s="61" t="inlineStr">
         <is>
           <t>Kanal</t>
         </is>
       </c>
-      <c r="C1" s="45" t="inlineStr">
+      <c r="C1" s="61" t="inlineStr">
         <is>
           <t>Kelas</t>
         </is>
       </c>
-      <c r="D1" s="45" t="inlineStr">
+      <c r="D1" s="61" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="E1" s="45" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="28">
-      <c r="A2" s="34" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="28">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>Zammad</t>
         </is>
       </c>
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="62" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="C2" s="34" t="inlineStr">
+      <c r="C2" s="62" t="inlineStr">
         <is>
           <t>Akses, firewall, VPN</t>
         </is>
       </c>
-      <c r="D2" s="34" t="inlineStr">
+      <c r="D2" s="62" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E2" s="34" t="inlineStr">
+      <c r="E2" s="62" t="inlineStr">
         <is>
           <t>Terbuka</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="28">
-      <c r="A3" s="34" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="28">
+      <c r="A3" s="62" t="inlineStr">
         <is>
           <t>Service Hub GLPI</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="62" t="inlineStr">
         <is>
           <t>Telepon</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="62" t="inlineStr">
         <is>
           <t>VM lifecycle</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="62" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="62" t="inlineStr">
         <is>
           <t>Ditangani</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="28">
-      <c r="B4" s="34" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="28">
+      <c r="A4" s="63" t="n"/>
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>Down atau performa</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="62" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="62" t="inlineStr">
         <is>
           <t>Menunggu pelanggan</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="28">
-      <c r="B5" s="34" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="28">
+      <c r="A5" s="63" t="n"/>
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>OTP atau email</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="D5" s="62" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
+      <c r="E5" s="62" t="inlineStr">
         <is>
           <t>Pulih</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="28">
-      <c r="B6" s="34" t="inlineStr">
+    <row r="6" ht="30" customHeight="1" s="28">
+      <c r="A6" s="63" t="n"/>
+      <c r="B6" s="62" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="62" t="inlineStr">
         <is>
           <t>Backup atau snapshot</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="D6" s="63" t="n"/>
+      <c r="E6" s="62" t="inlineStr">
         <is>
           <t>Ditutup</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="28">
-      <c r="B7" s="34" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1" s="28">
+      <c r="A7" s="63" t="n"/>
+      <c r="B7" s="62" t="inlineStr">
         <is>
           <t>Internal</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>SSL atau DNS</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="28">
-      <c r="C8" s="34" t="inlineStr">
+      <c r="D7" s="63" t="n"/>
+      <c r="E7" s="63" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="28">
+      <c r="A8" s="63" t="n"/>
+      <c r="B8" s="63" t="n"/>
+      <c r="C8" s="62" t="inlineStr">
         <is>
           <t>DC atau colo</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="28">
-      <c r="C9" s="34" t="inlineStr">
+      <c r="D8" s="63" t="n"/>
+      <c r="E8" s="63" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="28">
+      <c r="A9" s="63" t="n"/>
+      <c r="B9" s="63" t="n"/>
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="28">
-      <c r="C10" s="34" t="inlineStr">
+      <c r="D9" s="63" t="n"/>
+      <c r="E9" s="63" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="28">
+      <c r="A10" s="63" t="n"/>
+      <c r="B10" s="63" t="n"/>
+      <c r="C10" s="62" t="inlineStr">
         <is>
           <t>Keamanan (ke SOC)</t>
         </is>
       </c>
+      <c r="D10" s="63" t="n"/>
+      <c r="E10" s="63" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1468,21 +1645,27 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="27" min="1" max="1"/>
-    <col width="12" customWidth="1" style="27" min="2" max="2"/>
+    <col width="14" customWidth="1" style="27" min="2" max="2"/>
     <col width="16" customWidth="1" style="27" min="3" max="3"/>
     <col width="14" customWidth="1" style="27" min="4" max="4"/>
     <col width="11" customWidth="1" style="27" min="5" max="5"/>
     <col width="18" customWidth="1" style="27" min="6" max="6"/>
-    <col width="8" customWidth="1" style="27" min="7" max="7"/>
+    <col width="12" customWidth="1" style="27" min="7" max="7"/>
     <col width="30" customWidth="1" style="27" min="8" max="8"/>
     <col width="15" customWidth="1" style="27" min="9" max="12"/>
+    <col width="13" customWidth="1" style="28" min="10" max="10"/>
+    <col width="13" customWidth="1" style="28" min="11" max="11"/>
+    <col width="13" customWidth="1" style="28" min="12" max="12"/>
     <col width="14" customWidth="1" style="27" min="13" max="13"/>
     <col width="18" customWidth="1" style="27" min="14" max="14"/>
     <col width="26" customWidth="1" style="27" min="15" max="15"/>
     <col width="8" customWidth="1" style="27" min="16" max="16"/>
     <col width="12" customWidth="1" style="27" min="17" max="17"/>
     <col width="13" customWidth="1" style="27" min="18" max="18"/>
-    <col width="9" customWidth="1" style="27" min="19" max="22"/>
+    <col width="11" customWidth="1" style="27" min="19" max="22"/>
+    <col width="13" customWidth="1" style="28" min="20" max="20"/>
+    <col width="13" customWidth="1" style="28" min="21" max="21"/>
+    <col width="13" customWidth="1" style="28" min="22" max="22"/>
     <col width="18" customWidth="1" style="27" min="23" max="23"/>
   </cols>
   <sheetData>
@@ -1496,11 +1679,11 @@
     <row r="2" ht="15" customHeight="1" s="28">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>Kolom abu-abu dihitung otomatis. Tiket kelas Keamanan (ke SOC) diserahkan ke SOC; insidennya dicatat di SNX-ISMS-FRM-02. Tiket tanpa waktu Ack atau Pulih belum masuk persentase di sheet Ringkasan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" s="28">
+          <t>Kolom abu-abu terisi otomatis. Ticket kelas Keamanan diserahkan ke SOC, dan insidennya dicatat di SNX-ISMS-FRM-02. Ticket tanpa waktu Ack atau Pulih belum dihitung dalam persentase di sheet Ringkasan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="43.5" customHeight="1" s="28">
       <c r="A4" s="43" t="inlineStr">
         <is>
           <t>No tiket</t>
@@ -13696,7 +13879,7 @@
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -13704,19 +13887,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="40" customWidth="1" style="27" min="1" max="1"/>
     <col width="15" customWidth="1" style="27" min="2" max="7"/>
+    <col width="13" customWidth="1" style="28" min="3" max="3"/>
+    <col width="13" customWidth="1" style="28" min="4" max="4"/>
+    <col width="13" customWidth="1" style="28" min="5" max="5"/>
+    <col width="13" customWidth="1" style="28" min="6" max="6"/>
+    <col width="13" customWidth="1" style="28" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="28">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>Ringkasan tiket per periode</t>
+          <t>Ringkasan ticket per periode</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13928,7 @@
         <v>46356</v>
       </c>
     </row>
-    <row r="6" ht="23.85" customHeight="1" s="28">
+    <row r="6" ht="57" customHeight="1" s="28">
       <c r="A6" s="43" t="inlineStr">
         <is>
           <t>Severity</t>
@@ -13777,144 +13965,149 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="28">
-      <c r="A7" s="40" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1" s="28">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A7,Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A7,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="D7" s="50">
+      <c r="D7" s="64">
         <f>IF(COUNTIFS(Register!$G$5:$G$305,A7,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A7,Register!$U$5:$U$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))=0,"",C7/(COUNTIFS(Register!$G$5:$G$305,A7,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A7,Register!$U$5:$U$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))))</f>
         <v/>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A7,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="64">
         <f>IF(COUNTIFS(Register!$G$5:$G$305,A7,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A7,Register!$V$5:$V$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))=0,"",E7/(COUNTIFS(Register!$G$5:$G$305,A7,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A7,Register!$V$5:$V$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))))</f>
         <v/>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A7,Register!$P$5:$P$305,"Ya",Register!$Q$5:$Q$305,"",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="28">
-      <c r="A8" s="40" t="inlineStr">
+    <row r="8" ht="16.5" customHeight="1" s="28">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A8,Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A8,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="64">
         <f>IF(COUNTIFS(Register!$G$5:$G$305,A8,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A8,Register!$U$5:$U$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))=0,"",C8/(COUNTIFS(Register!$G$5:$G$305,A8,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A8,Register!$U$5:$U$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))))</f>
         <v/>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A8,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="F8" s="50">
+      <c r="F8" s="64">
         <f>IF(COUNTIFS(Register!$G$5:$G$305,A8,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A8,Register!$V$5:$V$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))=0,"",E8/(COUNTIFS(Register!$G$5:$G$305,A8,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A8,Register!$V$5:$V$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))))</f>
         <v/>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A8,Register!$P$5:$P$305,"Ya",Register!$Q$5:$Q$305,"",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="28">
-      <c r="A9" s="40" t="inlineStr">
+    <row r="9" ht="16.5" customHeight="1" s="28">
+      <c r="A9" s="59" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A9,Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A9,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="D9" s="50">
+      <c r="D9" s="64">
         <f>IF(COUNTIFS(Register!$G$5:$G$305,A9,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A9,Register!$U$5:$U$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))=0,"",C9/(COUNTIFS(Register!$G$5:$G$305,A9,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A9,Register!$U$5:$U$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))))</f>
         <v/>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A9,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="F9" s="50">
+      <c r="F9" s="64">
         <f>IF(COUNTIFS(Register!$G$5:$G$305,A9,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A9,Register!$V$5:$V$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))=0,"",E9/(COUNTIFS(Register!$G$5:$G$305,A9,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A9,Register!$V$5:$V$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))))</f>
         <v/>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A9,Register!$P$5:$P$305,"Ya",Register!$Q$5:$Q$305,"",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="28">
-      <c r="A10" s="40" t="inlineStr">
+    <row r="10" ht="16.5" customHeight="1" s="28">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B10" s="40">
+      <c r="B10" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A10,Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A10,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="64">
         <f>IF(COUNTIFS(Register!$G$5:$G$305,A10,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A10,Register!$U$5:$U$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))=0,"",C10/(COUNTIFS(Register!$G$5:$G$305,A10,Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A10,Register!$U$5:$U$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))))</f>
         <v/>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A10,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="64">
         <f>IF(COUNTIFS(Register!$G$5:$G$305,A10,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A10,Register!$V$5:$V$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))=0,"",E10/(COUNTIFS(Register!$G$5:$G$305,A10,Register!$V$5:$V$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,A10,Register!$V$5:$V$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))))</f>
         <v/>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="59">
         <f>COUNTIFS(Register!$G$5:$G$305,A10,Register!$P$5:$P$305,"Ya",Register!$Q$5:$Q$305,"",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="28">
-      <c r="A11" s="51" t="inlineStr">
+    <row r="11" ht="30" customHeight="1" s="28">
+      <c r="A11" s="65" t="inlineStr">
         <is>
           <t>P1 dan P2 di-ack sesuai target (KPI 95%)</t>
         </is>
       </c>
-      <c r="D11" s="52">
+      <c r="B11" s="63" t="n"/>
+      <c r="C11" s="63" t="n"/>
+      <c r="D11" s="66">
         <f>IF(B7+B8=0,"",(C7+C8)/(COUNTIFS(Register!$G$5:$G$305,"P1",Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,"P1",Register!$U$5:$U$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,"P2",Register!$U$5:$U$305,"Ya",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))+COUNTIFS(Register!$G$5:$G$305,"P2",Register!$U$5:$U$305,"Tidak",Register!$I$5:$I$305,"&gt;="&amp;$B$3,Register!$I$5:$I$305,"&lt;"&amp;($B$4+1))))</f>
         <v/>
       </c>
+      <c r="E11" s="63" t="n"/>
+      <c r="F11" s="63" t="n"/>
+      <c r="G11" s="63" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>